--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GriffithsR144\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87EB4CD-5029-43C1-8687-AD1454555B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FFBE287-DC4B-4970-9040-13B44EA8FEFA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -271,9 +271,6 @@
     <t>Beth yw Comed?</t>
   </si>
   <si>
-    <t>Beth y system blanedol?</t>
-  </si>
-  <si>
     <t>Beth yw Galaeth?</t>
   </si>
   <si>
@@ -368,6 +365,12 @@
   </si>
   <si>
     <t>Pelen o lwch a rhew sydd gydag orbit eliptigol iawn.</t>
+  </si>
+  <si>
+    <t>Beth yw system blanedol?</t>
+  </si>
+  <si>
+    <t>mudiantgwrthrych.png</t>
   </si>
 </sst>
 </file>
@@ -696,13 +699,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,7 +716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,7 +724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -729,7 +732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -737,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -745,7 +748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -753,10 +756,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -770,7 +773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -784,7 +787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -795,7 +798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -803,7 +806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -811,7 +814,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>28</v>
       </c>
@@ -819,7 +822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>30</v>
       </c>
@@ -827,7 +830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>35</v>
       </c>
@@ -835,7 +838,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>36</v>
       </c>
@@ -843,15 +846,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
     </row>
@@ -864,13 +867,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="58.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -881,7 +884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>32</v>
       </c>
@@ -892,7 +895,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -900,7 +903,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -908,7 +911,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -916,7 +919,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -924,7 +927,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -932,7 +935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -940,7 +943,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -948,7 +951,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -964,13 +967,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C49E91-841E-43E1-9E82-F658355D08D3}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="53.81640625" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>48</v>
       </c>
@@ -992,7 +995,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1032,10 +1035,10 @@
         <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -1054,22 +1057,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="1"/>
-    <col min="2" max="2" width="56.5703125" customWidth="1"/>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>67</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>71</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -1109,47 +1115,47 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1157,44 +1163,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1207,105 +1213,108 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="1"/>
-    <col min="2" max="2" width="56.5703125" customWidth="1"/>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="B5" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="B6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="11" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FFBE287-DC4B-4970-9040-13B44EA8FEFA}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0FE24BA-9CAD-495B-9430-AD7A22597B6E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="109">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -88,9 +88,6 @@
     <t>protoseren $\Rightarrow$ prif ddilyniant $\Rightarrow$ cawr coch $\Rightarrow$ corrach gwyn</t>
   </si>
   <si>
-    <t>mudiant gwrthrych.png</t>
-  </si>
-  <si>
     <t>Disgrifiwch mudiant y bws yn rhan B</t>
   </si>
   <si>
@@ -361,16 +358,16 @@
     <t>Sawl proton a niwtron sydd mewn niwclews $\ce{^210_82Pb}$?</t>
   </si>
   <si>
-    <t>arbrawf ymestyn sbring.png</t>
-  </si>
-  <si>
     <t>Pelen o lwch a rhew sydd gydag orbit eliptigol iawn.</t>
   </si>
   <si>
     <t>Beth yw system blanedol?</t>
   </si>
   <si>
-    <t>mudiantgwrthrych.png</t>
+    <t>mudiant_gwrthrych.png</t>
+  </si>
+  <si>
+    <t>arbrawf_ymestyn_sbring.png</t>
   </si>
 </sst>
 </file>
@@ -394,12 +391,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -426,6 +417,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -473,11 +470,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -745,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -755,95 +752,95 @@
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>109</v>
+      <c r="C6" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>26</v>
+      <c r="C8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -885,78 +882,78 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +967,7 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.81640625" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,65 +982,66 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>33</v>
+      <c r="B2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>106</v>
+      <c r="C7" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
         <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1077,82 +1075,82 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>74</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,10 +1163,10 @@
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1176,31 +1174,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1233,58 +1231,58 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="11" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0FE24BA-9CAD-495B-9430-AD7A22597B6E}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49458FB7-63BC-4A62-B0A0-E394DFFDC0ED}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
     <sheet name="6.2 Deddfau Newton" sheetId="3" r:id="rId2"/>
     <sheet name="6.3  Gwaith ac Egni" sheetId="4" r:id="rId3"/>
-    <sheet name="6.4 Sêr a phlanedau" sheetId="2" r:id="rId4"/>
-    <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId5"/>
+    <sheet name="2.4 Cysyniadau pellach mudiant" sheetId="6" r:id="rId4"/>
+    <sheet name="6.4 Sêr a phlanedau" sheetId="2" r:id="rId5"/>
+    <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -368,6 +369,78 @@
   </si>
   <si>
     <t>arbrawf_ymestyn_sbring.png</t>
+  </si>
+  <si>
+    <t>Sut mae gwregys diogelwch yn amddiffyn gyrrwr yn ystod gwrthdrawiad.</t>
+  </si>
+  <si>
+    <t>Cyfrifo graddiant y graff.</t>
+  </si>
+  <si>
+    <t>Sut mae cyfrifo cyflymiad o graff cyflymder-amser?</t>
+  </si>
+  <si>
+    <t>Sut mae cyfrifo pellter a deithiwyd o graff cyflymder-amser? (UWCH YN UNIG)</t>
+  </si>
+  <si>
+    <t>Cyfrifo arwynebedd o dan y graff</t>
+  </si>
+  <si>
+    <t>Wrth i'r gwrthrych gyflymu, mae'r gwrthiant aer arno yn cynyddu nes bod y gwrthiant aer a'i bwysau yn cydbwyso ac felly y grym cydeffaith yn sero.</t>
+  </si>
+  <si>
+    <t>Sut mae gwrthrych sy'n syrthio drwy'r aer( e.e. cas cacen neu plymiwr awyr) yn cyrraedd buanedd terfynol?</t>
+  </si>
+  <si>
+    <t>Nodwch yr uned ar gyfer moment grym</t>
+  </si>
+  <si>
+    <t>Nm</t>
+  </si>
+  <si>
+    <t>Nodwch yr egwyddor momentau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan mae gwrthrych (e.e. riwl fetr) mewn cydbwysedd, mae swm y momentau clocwedd o amgylch y colyn yn hafal i swm y momentau gwrthglocwedd. </t>
+  </si>
+  <si>
+    <t>Sut mae bag aer yn helpu i gadw teithwyr yn ddiogel  yn ystod gwrthdrawiad.</t>
+  </si>
+  <si>
+    <t>Nodwch egwyddor cadwraeth momentwm.</t>
+  </si>
+  <si>
+    <t>Cyfanswm momentwm cyn gwrthdrawiad = cyfanswm momentwm ar ôl gwrthdrawiad os nad oes grymoedd allanol yn gweithredu.</t>
+  </si>
+  <si>
+    <t>Nodwch yr uned ar gyfer momentwm</t>
+  </si>
+  <si>
+    <t>$kg m s^-1$ neu kg m/s</t>
+  </si>
+  <si>
+    <t>Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
+  </si>
+  <si>
+    <t>Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys.</t>
+  </si>
+  <si>
+    <t>Pan fydd hydrogen yn gostwng, bydd y seren yn dechrau ymasu heliwm.</t>
+  </si>
+  <si>
+    <t>Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn orgawr coch.</t>
+  </si>
+  <si>
+    <t>Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu.</t>
+  </si>
+  <si>
+    <t>Mae'r seren wedyn yn ffrwydro mewn uwchnofa gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae seren niwtron dwys iawn neu dwll du ar ôl.</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
+  </si>
+  <si>
+    <t>$\begin{itemize} \item Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
   </si>
 </sst>
 </file>
@@ -695,7 +768,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.26953125" customWidth="1"/>
@@ -844,16 +917,36 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -863,7 +956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.453125" customWidth="1"/>
@@ -954,6 +1047,14 @@
       </c>
       <c r="B10" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1051,11 +1152,78 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808CBEAB-1A82-4D21-9D60-79ED5AE8D7ED}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="53.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
@@ -1193,12 +1361,50 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1206,7 +1412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEBD08B-1771-4930-875D-750DA6CE58B7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49458FB7-63BC-4A62-B0A0-E394DFFDC0ED}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16292BD0-05D7-4028-B46D-A78641FAD77A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,7 +440,7 @@
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>$\begin{itemize} \item Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
+    <t>$\begin{itemize} \item Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.$</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16292BD0-05D7-4028-B46D-A78641FAD77A}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FB0197-9728-4854-8C28-34A7AFB0E3C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,7 +440,7 @@
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>$\begin{itemize} \item Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.$</t>
+    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio $\textbf{protoseren}$. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FB0197-9728-4854-8C28-34A7AFB0E3C4}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E046351-F5B5-4E4D-8C19-AD933F935B23}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,7 +440,7 @@
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio $\textbf{protoseren}$. \item Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
+    <t>$Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren \textbf{prif ddilyniant} fawr. $</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E046351-F5B5-4E4D-8C19-AD933F935B23}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C0A798-11A6-4DEA-B12A-839A7571B28A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="127">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -419,28 +419,10 @@
     <t>$kg m s^-1$ neu kg m/s</t>
   </si>
   <si>
-    <t>Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren prif ddilyniant fawr.</t>
-  </si>
-  <si>
-    <t>Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys.</t>
-  </si>
-  <si>
-    <t>Pan fydd hydrogen yn gostwng, bydd y seren yn dechrau ymasu heliwm.</t>
-  </si>
-  <si>
-    <t>Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn orgawr coch.</t>
-  </si>
-  <si>
-    <t>Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu.</t>
-  </si>
-  <si>
-    <t>Mae'r seren wedyn yn ffrwydro mewn uwchnofa gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae seren niwtron dwys iawn neu dwll du ar ôl.</t>
-  </si>
-  <si>
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>$Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio \textbf{protoseren}. Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren \textbf{prif ddilyniant} fawr. $</t>
+    <t>$Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb {protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du$ ar ôl.</t>
   </si>
 </sst>
 </file>
@@ -1223,7 +1205,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
@@ -1361,7 +1343,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>90</v>
       </c>
@@ -1369,42 +1351,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C0A798-11A6-4DEA-B12A-839A7571B28A}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BD593E8-708B-4775-BC1D-B27D26D08587}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,7 +422,7 @@
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>$Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb {protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du$ ar ôl.</t>
+    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb {protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du$ ar ôl.</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BD593E8-708B-4775-BC1D-B27D26D08587}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54B7ACE-C73E-4F21-ADCE-40C33E67AAF1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,9 +308,6 @@
     <t>O beth ddechreuodd cysawd yr Haul?</t>
   </si>
   <si>
-    <t>Cwmwl o nwy a llwch.</t>
-  </si>
-  <si>
     <t>Uwchnofa</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb {protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du$ ar ôl.</t>
+  </si>
+  <si>
+    <t>Cwmwl o nwy a llwch yn cwympo (collapse) oherwydd disgyrchiant.</t>
   </si>
 </sst>
 </file>
@@ -808,7 +808,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -819,7 +819,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>23</v>
@@ -833,7 +833,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>25</v>
@@ -847,7 +847,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -900,7 +900,7 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>30</v>
@@ -908,23 +908,23 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>30</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1116,7 @@
         <v>61</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>32</v>
@@ -1166,26 +1166,26 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
         <v>118</v>
-      </c>
-      <c r="B3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" t="s">
         <v>121</v>
-      </c>
-      <c r="B4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" t="s">
         <v>123</v>
-      </c>
-      <c r="B5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
         <v>74</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1297,7 +1297,7 @@
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
         <v>77</v>
@@ -1340,23 +1340,23 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" t="s">
         <v>125</v>
-      </c>
-      <c r="B18" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1389,58 +1389,58 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54B7ACE-C73E-4F21-ADCE-40C33E67AAF1}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B09D5D-08A2-4A4E-B72F-C2031D468D7B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -419,10 +419,10 @@
     <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
   </si>
   <si>
-    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb {protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du$ ar ôl.</t>
-  </si>
-  <si>
     <t>Cwmwl o nwy a llwch yn cwympo (collapse) oherwydd disgyrchiant.</t>
+  </si>
+  <si>
+    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du}$ ar ôl.</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1340,7 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1356,7 +1356,7 @@
         <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B09D5D-08A2-4A4E-B72F-C2031D468D7B}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70E540C5-B17D-4B89-954C-63BE7442B9F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,7 +422,7 @@
     <t>Cwmwl o nwy a llwch yn cwympo (collapse) oherwydd disgyrchiant.</t>
   </si>
   <si>
-    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio ${\textb protoseren}.$ Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren ${\textbf prif ddilyniant}$ fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ${\textbf orgawr coch}.$ Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn ${\textbf uwchnofa}$ gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae ${\textbf seren niwtron}$ dwys iawn neu ${\textbf dwll du}$ ar ôl.</t>
+    <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio PROTOSEREN. Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren PRIF DDILYNIANT fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ORGAWR COCH. Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn UWCHNOFA gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae SEREN NIWTRON dwys iawn neu TWLL DU ar ôl.</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70E540C5-B17D-4B89-954C-63BE7442B9F4}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0017D2B1-31A1-43C8-B229-58D0D6BB5B49}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="6.3  Gwaith ac Egni" sheetId="4" r:id="rId3"/>
     <sheet name="2.4 Cysyniadau pellach mudiant" sheetId="6" r:id="rId4"/>
     <sheet name="6.4 Sêr a phlanedau" sheetId="2" r:id="rId5"/>
-    <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId6"/>
+    <sheet name="2.6 Y Bydysawd" sheetId="7" r:id="rId6"/>
+    <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="130">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -416,20 +417,29 @@
     <t>$kg m s^-1$ neu kg m/s</t>
   </si>
   <si>
-    <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr cawr hyn o’u geni hyd eu marw.</t>
-  </si>
-  <si>
     <t>Cwmwl o nwy a llwch yn cwympo (collapse) oherwydd disgyrchiant.</t>
   </si>
   <si>
     <t>Mae nwy a llwch yn cael eu tynnu at ei gilydd gan ddisgyrchiant i ffurfio PROTOSEREN. Mae niwclysau hydrogen yn ymasu i ffurfio heliwm, gan gynhyrchu seren PRIF DDILYNIANT fawr.  Yn y cyflwr sefydlog mae grym mewnol disgyrchiant a grym tuag allan gwasgedd nwy a phelydriad yn dod yn gytbwys. Pan fydd hydrogen yn rhedeg allan, bydd y seren yn dechrau ymasu heliwm. Mae'r grymoedd yn mynd yn anghytbwys ac mae'r seren yn ehangu gan ddod yn ORGAWR COCH. Yn y pen draw, pan fydd ymasiad yn dod i ben, mae'r grym disgyrchiant yn fwy na'r gwasgedd pelydriad ac mae'r seren yn crebachu. Mae'r seren wedyn yn ffrwydro mewn UWCHNOFA gan fwrw elfennau mwy trwm allan i'r gofod, ac yn ei chanol, mae SEREN NIWTRON dwys iawn neu TWLL DU ar ôl.</t>
+  </si>
+  <si>
+    <t>Disgrifiwch ac esboniwch gylchred oes (life cycle) y sêr llawer mwy na'r HAUL o’u geni hyd eu marw.</t>
+  </si>
+  <si>
+    <t>sbectrwm_llinell_amsugno.png</t>
+  </si>
+  <si>
+    <t>Sut mae’r llinellau du’n cael eu ffurfio?</t>
+  </si>
+  <si>
+    <t>Atomau nwy/elfennau yn atmosffer y sêr o'r galaeth sy'n amsugno golau gyda tonfeddi penodol.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -479,6 +489,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -513,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -532,6 +549,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1340,7 +1358,7 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1353,10 +1371,10 @@
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1365,6 +1383,105 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664308B1-3772-4209-9FCF-E0C389C26103}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="10"/>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEBD08B-1771-4930-875D-750DA6CE58B7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0017D2B1-31A1-43C8-B229-58D0D6BB5B49}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8868BA-7F61-4F32-A969-E8268D1662B7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -433,13 +433,37 @@
   </si>
   <si>
     <t>Atomau nwy/elfennau yn atmosffer y sêr o'r galaeth sy'n amsugno golau gyda tonfeddi penodol.</t>
+  </si>
+  <si>
+    <t>Sut mae astudio sbectra fel hyn o alaethau pell yn cefnogi model y Glec Fawr?</t>
+  </si>
+  <si>
+    <t>Nodwch y ddau ddarn o dystiolaeth sy’n cefnogi model y Glec Fawr am ddechreuad y Bydysawd.</t>
+  </si>
+  <si>
+    <t>Pelydriad Cefndir Microdonnau Cosmig (CMBR) a Rhuddiad</t>
+  </si>
+  <si>
+    <t>Maen nhw i gyd yn dangos rhuddiad (llinellau wedi symud i ochr coch) oherwydd bod y galaethau yn symud i ffwrdd oddi wrthon ni. Mae'r Bydysawd wedi ehangu dros amser felly mae'n rhaid ei fod wedi dechrau o un pwynt (Y Glec Fawr).</t>
+  </si>
+  <si>
+    <t>Beth yw'r pelydriad cefndir microdonnau cosmig (CMBR)?</t>
+  </si>
+  <si>
+    <t>Yn ystod y Glec Fawr cafodd pelydrau gama egni uchel a tonfedd fer eu rhyddhau. Wrth i'r Bydysawd ehangu mae tonfedd y pelydrau yma wedi ymestyn, erbyn heddiw mae eu tonfedd wedi ymestyn fel eu bod yn y rhan microdon o'r sbectrwm electromagnetig.</t>
+  </si>
+  <si>
+    <t>CMBR.png</t>
+  </si>
+  <si>
+    <t>Beth yw gwerthoedd a a b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -496,6 +520,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF323F52"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -530,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -550,6 +588,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1417,17 +1457,34 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="10"/>
+      <c r="A5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1560,6 +1617,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8868BA-7F61-4F32-A969-E8268D1662B7}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D67BE03-8504-4AA3-9E28-82E0F8FBF224}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -456,14 +456,60 @@
     <t>CMBR.png</t>
   </si>
   <si>
-    <t>Beth yw gwerthoedd a a b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
+    <r>
+      <t xml:space="preserve">Beth yw gwerthoedd </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\newline \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -530,6 +576,15 @@
     <font>
       <sz val="10"/>
       <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1617,7 +1672,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>137</v>
       </c>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D67BE03-8504-4AA3-9E28-82E0F8FBF224}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68FEFFB4-8A50-4310-9E42-7A4180FE4F24}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="151">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -456,60 +456,53 @@
     <t>CMBR.png</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Beth yw gwerthoedd </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>a,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\newline \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
-    </r>
+    <t>a = 237, b = 93</t>
+  </si>
+  <si>
+    <t>ymbelydredd_cefndir.png</t>
+  </si>
+  <si>
+    <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $ \\ \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
+  </si>
+  <si>
+    <t>Mae’r siart cylch yn dangos ffynonellau sy'n cyfrannu at ymbelyredd cefndir. Pa ffynonellau sy'n naturiol?</t>
+  </si>
+  <si>
+    <t>nwy radon, tir ac adeiladau, pelydrau cosmig,bwyd a diod</t>
+  </si>
+  <si>
+    <t>Mae’r siart cylch yn dangos ffynonellau sy'n cyfrannu at ymbelyredd cefndir. Pa ffynonellau sy'n rhai gwneud (man-made)?</t>
+  </si>
+  <si>
+    <t>Meddygol, pŵer ac arfau niwclear</t>
+  </si>
+  <si>
+    <t>Beth yw ystyr y term 'isotopau'?</t>
+  </si>
+  <si>
+    <t>Atomau o yr un elfen sydd gyda'r un nifer o brotonau ond nifer gwahanol o niwtronau.</t>
+  </si>
+  <si>
+    <t>Pam mae rhai isotopau yn ymbelydrol?</t>
+  </si>
+  <si>
+    <t>Anghydbwysedd rhwng nifer y protonau a'r niwtronau felly mae’r niwclews yn ansefydlog.</t>
+  </si>
+  <si>
+    <t>symbolau_ymbelydredd.png</t>
+  </si>
+  <si>
+    <t>Enwch y math o ymbelydredd.</t>
+  </si>
+  <si>
+    <t>Alffa -  $\ce{^4_2\alpha} \\$, Beta - $ \ce{^0_-1\beta} \\$, Gama - $ \gamma$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -576,15 +569,6 @@
     <font>
       <sz val="10"/>
       <color theme="4"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1598,7 +1582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
@@ -1642,59 +1626,92 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>97</v>
+        <v>150</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-    </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
+      <c r="A11" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -1708,7 +1725,12 @@
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68FEFFB4-8A50-4310-9E42-7A4180FE4F24}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FFDA416-9337-40A4-96A2-C35CB47603BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,9 +462,6 @@
     <t>ymbelydredd_cefndir.png</t>
   </si>
   <si>
-    <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $ \\ \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
-  </si>
-  <si>
     <t>Mae’r siart cylch yn dangos ffynonellau sy'n cyfrannu at ymbelyredd cefndir. Pa ffynonellau sy'n naturiol?</t>
   </si>
   <si>
@@ -496,6 +493,9 @@
   </si>
   <si>
     <t>Alffa -  $\ce{^4_2\alpha} \\$, Beta - $ \ce{^0_-1\beta} \\$, Gama - $ \gamma$</t>
+  </si>
+  <si>
+    <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\break \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
   </si>
 </sst>
 </file>
@@ -1626,13 +1626,13 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>150</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1667,9 +1667,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>137</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>138</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>138</v>
@@ -1699,18 +1699,18 @@
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FFDA416-9337-40A4-96A2-C35CB47603BA}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71ABB68B-F15E-4AF5-9DB6-DC61AD5D1594}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,7 +495,7 @@
     <t>Alffa -  $\ce{^4_2\alpha} \\$, Beta - $ \ce{^0_-1\beta} \\$, Gama - $ \gamma$</t>
   </si>
   <si>
-    <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear $\break \ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
+    <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear &lt;br&gt; &lt;br&gt; $\ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71ABB68B-F15E-4AF5-9DB6-DC61AD5D1594}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93CC5BA0-37BD-4A58-BD5B-AC62B96D78FF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="6.4 Sêr a phlanedau" sheetId="2" r:id="rId5"/>
     <sheet name="2.6 Y Bydysawd" sheetId="7" r:id="rId6"/>
     <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId7"/>
+    <sheet name="6.6 Hanner Oes" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="157">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -228,9 +229,6 @@
     <t>Disgrifiwch sut mae’r cyfarpar sydd i’w weld isod yn cael ei ddefnyddio i ymchwilio i estyniad sbring.</t>
   </si>
   <si>
-    <t>Gosod y clamp. Hongian y sbring o'r clamp.  Rhoi pren mesur yn ei le [fertigol] wrth ochr y sbring. Cofnodi hyd gwreiddiol y sbring.Cysylltu'r hongiwr màs 100g. Ychwanegu 100 g arall at y sbring a chofnodi'r hyd newydd. Ailadrodd nes bod pob màs wedi'i ychwanegu. Cymryd ailddarlleniadau/ailadrodd darlleniadau. Cyfrifo'r hyd cymedrig ar gyfer pob màs sydd wedi’i ychwanegu. Cyfrifo'r estyniad ar gyfer pob màs sydd wedi’i ychwanegu. Plotio graff grym / màs yn erbyn estyniad.</t>
-  </si>
-  <si>
     <t>Sawl Joule sydd mewn 1 kJ (kiloJoule)?</t>
   </si>
   <si>
@@ -492,10 +490,31 @@
     <t>Enwch y math o ymbelydredd.</t>
   </si>
   <si>
-    <t>Alffa -  $\ce{^4_2\alpha} \\$, Beta - $ \ce{^0_-1\beta} \\$, Gama - $ \gamma$</t>
-  </si>
-  <si>
     <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear &lt;br&gt; &lt;br&gt; $\ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
+  </si>
+  <si>
+    <t>Alffa -  $\ce{^4_2\alpha}$ &lt;br&gt; Beta - $\ce{^0_-1\beta} $ &lt;br&gt; Gama - $\gamma$</t>
+  </si>
+  <si>
+    <t>papur, alwminiwm tenau a plwm trwchus</t>
+  </si>
+  <si>
+    <t>alwminiwm tenau a plwm trwchus</t>
+  </si>
+  <si>
+    <t>plwm trwchus yn unig</t>
+  </si>
+  <si>
+    <t>Pa amsugnyddion (papur, alwminiwm tenau, plwm trwchus) wnaiff leihau cyfradd cyfrif o ffynhonnell alffa?</t>
+  </si>
+  <si>
+    <t>Pa amsugnyddion (papur, alwminiwm tenau, plwm trwchus) wnaiff leihau cyfradd cyfrif o ffynhonnell beta?</t>
+  </si>
+  <si>
+    <t>Pa amsugnydd (papur, alwminiwm tenau, plwm trwchus) wnaiff leihau cyfradd cyfrif o ffynhonnell gama?</t>
+  </si>
+  <si>
+    <t>Gosod y clamp. Hongian y sbring o'r clamp.  &lt;br&gt;Rhoi pren mesur yn ei le [fertigol] wrth ochr y sbring. &lt;br&gt;Cofnodi hyd gwreiddiol y sbring.&lt;br&gt;Cysylltu'r hongiwr màs 100g. &lt;br&gt;Ychwanegu 100 g arall at y sbring a chofnodi'r hyd newydd. &lt;br&gt;Ailadrodd nes bod pob màs wedi'i ychwanegu. &lt;br&gt;Cymryd ailddarlleniadau/ailadrodd darlleniadau. &lt;br&gt;Cyfrifo'r hyd cymedrig ar gyfer pob màs sydd wedi’i ychwanegu. &lt;br&gt;Cyfrifo'r estyniad ar gyfer pob màs sydd wedi’i ychwanegu.&lt;br&gt; Plotio graff grym / màs yn erbyn estyniad.</t>
   </si>
 </sst>
 </file>
@@ -905,7 +924,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -916,7 +935,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>23</v>
@@ -930,7 +949,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>25</v>
@@ -944,7 +963,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -997,7 +1016,7 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>30</v>
@@ -1005,23 +1024,23 @@
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>30</v>
@@ -1130,10 +1149,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1210,18 +1229,18 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
         <v>62</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1252,10 +1271,10 @@
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>32</v>
@@ -1263,26 +1282,26 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" t="s">
         <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
         <v>120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
         <v>122</v>
-      </c>
-      <c r="B5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1322,82 +1341,82 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1410,10 +1429,10 @@
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1421,39 +1440,39 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1486,43 +1505,43 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>129</v>
-      </c>
       <c r="C2" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1582,7 +1601,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
@@ -1602,132 +1621,344 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>149</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>97</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>99</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>101</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>150</v>
+      <c r="A10" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>143</v>
+      <c r="A13" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBB8F5A-0EA2-453D-A2D2-FF146DBE383B}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="14"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="14"/>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93CC5BA0-37BD-4A58-BD5B-AC62B96D78FF}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16029E74-5E11-4066-A01B-429AC60C718F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="167">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -493,9 +493,6 @@
     <t>Beth yw gwerthoedd a, b er mwyn cwblhau'r hafaliad dadfeiliad niwclear &lt;br&gt; &lt;br&gt; $\ce{^241_95Am -&gt; ^a_bNp + ^4_2\alpha}$?</t>
   </si>
   <si>
-    <t>Alffa -  $\ce{^4_2\alpha}$ &lt;br&gt; Beta - $\ce{^0_-1\beta} $ &lt;br&gt; Gama - $\gamma$</t>
-  </si>
-  <si>
     <t>papur, alwminiwm tenau a plwm trwchus</t>
   </si>
   <si>
@@ -515,6 +512,39 @@
   </si>
   <si>
     <t>Gosod y clamp. Hongian y sbring o'r clamp.  &lt;br&gt;Rhoi pren mesur yn ei le [fertigol] wrth ochr y sbring. &lt;br&gt;Cofnodi hyd gwreiddiol y sbring.&lt;br&gt;Cysylltu'r hongiwr màs 100g. &lt;br&gt;Ychwanegu 100 g arall at y sbring a chofnodi'r hyd newydd. &lt;br&gt;Ailadrodd nes bod pob màs wedi'i ychwanegu. &lt;br&gt;Cymryd ailddarlleniadau/ailadrodd darlleniadau. &lt;br&gt;Cyfrifo'r hyd cymedrig ar gyfer pob màs sydd wedi’i ychwanegu. &lt;br&gt;Cyfrifo'r estyniad ar gyfer pob màs sydd wedi’i ychwanegu.&lt;br&gt; Plotio graff grym / màs yn erbyn estyniad.</t>
+  </si>
+  <si>
+    <t>Alffa -  $\ce{^4_2\alpha}$ &lt;br&gt;&lt;br&gt; Beta - $\ce{^0_-1\beta} $ &lt;br&gt;&lt;br&gt; Gama - $\gamma$</t>
+  </si>
+  <si>
+    <t>Beth yw diffiniad hanner oes?</t>
+  </si>
+  <si>
+    <t>Yr amser y mae'n ei gymryd i fàs yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol. &lt;br&gt; neu&lt;br&gt; Yr amser y mae'n ei gymryd i'r actifedd leihau i hanner ei werth cychwynnol. &lt;br&gt; neu &lt;br&gt; Yr amser y mae'n ei gymryd i nifer y niwclysau yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol</t>
+  </si>
+  <si>
+    <t>Os oes 800 o niwclysau ymbelydrol i gychwyn, sawl niwclysau ymbelydrol sydd yn weddill ar ôl 1 hanner oes?</t>
+  </si>
+  <si>
+    <t>Os oes 1400 o niwclysau ymbelydrol i gychwyn, sawl niwclysau ymbelydrol sydd yn weddill ar ôl 2 hanner oes?</t>
+  </si>
+  <si>
+    <t>1400 $\Rightarrow$ 700 $\Rightarrow$ 350</t>
+  </si>
+  <si>
+    <t>800 $\Rightarrow$ 400</t>
+  </si>
+  <si>
+    <t>Beth fydd ffracsiwn y niwclysau ymbelydrol sy'n weddill  ar ôl 3 hanner oes?</t>
+  </si>
+  <si>
+    <t>1 $\Rightarrow \frac{1}{2}  \Rightarrow \frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>Mae gan isotop ymbelydrol hanner oes o 5 mlynedd. Beth yw'r canran sy'n weddill ar ôl 10 mlynedd?</t>
+  </si>
+  <si>
+    <t>100% $\Rightarrow$ 50% $\Rightarrow$ 25%</t>
   </si>
 </sst>
 </file>
@@ -626,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -648,6 +678,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1229,7 +1260,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>106</v>
@@ -1423,7 +1454,7 @@
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1648,7 +1679,7 @@
         <v>147</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>146</v>
@@ -1656,28 +1687,28 @@
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="14"/>
     </row>
@@ -1806,143 +1837,93 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>92</v>
+      <c r="A3" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>93</v>
+      <c r="A4" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>147</v>
+      <c r="A5" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>146</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>150</v>
+      <c r="A6" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>151</v>
-      </c>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>152</v>
-      </c>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>96</v>
-      </c>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>98</v>
-      </c>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>100</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>101</v>
-      </c>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>136</v>
-      </c>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>137</v>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="14"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>137</v>
-      </c>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>143</v>
-      </c>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>145</v>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16029E74-5E11-4066-A01B-429AC60C718F}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E913404-6116-4017-A8EF-3749AC16ECCF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,9 +520,6 @@
     <t>Beth yw diffiniad hanner oes?</t>
   </si>
   <si>
-    <t>Yr amser y mae'n ei gymryd i fàs yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol. &lt;br&gt; neu&lt;br&gt; Yr amser y mae'n ei gymryd i'r actifedd leihau i hanner ei werth cychwynnol. &lt;br&gt; neu &lt;br&gt; Yr amser y mae'n ei gymryd i nifer y niwclysau yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol</t>
-  </si>
-  <si>
     <t>Os oes 800 o niwclysau ymbelydrol i gychwyn, sawl niwclysau ymbelydrol sydd yn weddill ar ôl 1 hanner oes?</t>
   </si>
   <si>
@@ -545,6 +542,9 @@
   </si>
   <si>
     <t>100% $\Rightarrow$ 50% $\Rightarrow$ 25%</t>
+  </si>
+  <si>
+    <t>Yr amser y mae'n ei gymryd i fàs yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol. &lt;br&gt;&lt;br&gt; neu&lt;br&gt;&lt;br&gt; Yr amser y mae'n ei gymryd i'r actifedd leihau i hanner ei werth cychwynnol. &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt; Yr amser y mae'n ei gymryd i nifer y niwclysau yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol</t>
   </si>
 </sst>
 </file>
@@ -1840,40 +1840,40 @@
         <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>165</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>166</v>
       </c>
       <c r="C6" s="14"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E913404-6116-4017-A8EF-3749AC16ECCF}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFF58207-B2FD-41C0-87C3-B1F0E02B1A69}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="2.6 Y Bydysawd" sheetId="7" r:id="rId6"/>
     <sheet name="6.5 Mathau o belydriad" sheetId="5" r:id="rId7"/>
     <sheet name="6.6 Hanner Oes" sheetId="8" r:id="rId8"/>
+    <sheet name="2.9 Egni Niwclear" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="188">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -545,6 +546,69 @@
   </si>
   <si>
     <t>Yr amser y mae'n ei gymryd i fàs yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol. &lt;br&gt;&lt;br&gt; neu&lt;br&gt;&lt;br&gt; Yr amser y mae'n ei gymryd i'r actifedd leihau i hanner ei werth cychwynnol. &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt; Yr amser y mae'n ei gymryd i nifer y niwclysau yr elfen ymbelydrol wreiddiol leihau i hanner ei werth cychwynnol</t>
+  </si>
+  <si>
+    <t>Beth yw swyddogaeth (function) cymedrolydd mewn adweithydd niwclear?</t>
+  </si>
+  <si>
+    <t>adweithydd_ymholltiad.png</t>
+  </si>
+  <si>
+    <t>Mae'n arafu niwtronau fel eu bod yn gallu cael eu hamsugno gan niwclews U-235.</t>
+  </si>
+  <si>
+    <t>Beth yw ymholltiad niwclear?</t>
+  </si>
+  <si>
+    <t>Pan mae niwclews mawr fel wraniwm-235 yn amsugno niwtron araf bydd yn troi yn ansefydlog, hollti i niwclysau llai, rhyddhau egni a 2/3 o niwtronau.</t>
+  </si>
+  <si>
+    <t>Beth yw rôl rhodenni rheoli mewn adweithydd niwclear?</t>
+  </si>
+  <si>
+    <t>Mae rhodenni rheoli'n amsugno niwtronau fel bod adwaith ymholltiad ar gyfartaledd yn arwain at un ymholltiad pellach ac felly yn atal adwaith cadwynol afreolus. Maen nhw'n gallu cael eu codi ac / neu eu gostwng i reoli cyfradd yr adwaith.</t>
+  </si>
+  <si>
+    <t>Beth yw ymasiad niwclear?</t>
+  </si>
+  <si>
+    <t>Pam mae’n anodd cyflawni ymasiad niwclear ar y Ddaear?</t>
+  </si>
+  <si>
+    <t>Angen tymheredd/egni  uchel iawn. &lt;br&gt; Angen gwasgedd uchel. &lt;br&gt; Angen i niwclysau gael digon o egni i fynd digon agos iw'r gilydd a chyfuno.</t>
+  </si>
+  <si>
+    <t>Pan gaiff dau niwclews bach fel hydrogen eu cyfuno â'i gilydd i greu un niwclews mwy fel heliwm.</t>
+  </si>
+  <si>
+    <t>Beth yw manteision ymasiad niwclear o’i gymharu ag ymholltiad niwclear?</t>
+  </si>
+  <si>
+    <t>Pam mae’n anodd storio gwastraff ymbelydrol yn ddiogel?</t>
+  </si>
+  <si>
+    <t>Mae gan y gwastraff ymbelydrol hanner oes hir iawn felly mae'n beryglu am amser hir iawn. &lt;br&gt; Mae'r gwastaff yn allyrru pelydriad (alffa/beta/gama) sy'n  ioneiddio'n gryf  neu gyda phŵer treiddio uchel.</t>
+  </si>
+  <si>
+    <t>Ymasiad ddim yn cynhyrchu gwastraff ymbelydrol gyda hanner oes hir.  Am bob cilogram, mae ymasiad yn cynhyrchu mwy o egni nag ymholltiad.</t>
+  </si>
+  <si>
+    <t>adwaith_ymholltiad.png</t>
+  </si>
+  <si>
+    <t>Cwblhewch yr hafaliad ar gyfer ymholltiad niwclear.</t>
+  </si>
+  <si>
+    <t>2 $\ce{^1_0n}$? &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt;  $\ce{^1_0n + ^1_0n}$</t>
+  </si>
+  <si>
+    <t>adwaith_ymasiad.png</t>
+  </si>
+  <si>
+    <t>Ysgrifennwch hafaliad niwclear cytbwys ar gyfer ymasiad dewteriwm a thritiwm.</t>
+  </si>
+  <si>
+    <t>$\ce{^2_1H +^3_1H -&gt; ^4_2He + ^1_0n}$</t>
   </si>
 </sst>
 </file>
@@ -1945,4 +2009,179 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{422A3C2A-D033-4FC1-B4A4-17A49215C36D}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="14"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="14"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="10"/>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="14"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="14"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFF58207-B2FD-41C0-87C3-B1F0E02B1A69}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5AE76CD-58DE-43F1-84E2-E8C0215092A9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,9 +575,6 @@
     <t>Pam mae’n anodd cyflawni ymasiad niwclear ar y Ddaear?</t>
   </si>
   <si>
-    <t>Angen tymheredd/egni  uchel iawn. &lt;br&gt; Angen gwasgedd uchel. &lt;br&gt; Angen i niwclysau gael digon o egni i fynd digon agos iw'r gilydd a chyfuno.</t>
-  </si>
-  <si>
     <t>Pan gaiff dau niwclews bach fel hydrogen eu cyfuno â'i gilydd i greu un niwclews mwy fel heliwm.</t>
   </si>
   <si>
@@ -587,21 +584,12 @@
     <t>Pam mae’n anodd storio gwastraff ymbelydrol yn ddiogel?</t>
   </si>
   <si>
-    <t>Mae gan y gwastraff ymbelydrol hanner oes hir iawn felly mae'n beryglu am amser hir iawn. &lt;br&gt; Mae'r gwastaff yn allyrru pelydriad (alffa/beta/gama) sy'n  ioneiddio'n gryf  neu gyda phŵer treiddio uchel.</t>
-  </si>
-  <si>
-    <t>Ymasiad ddim yn cynhyrchu gwastraff ymbelydrol gyda hanner oes hir.  Am bob cilogram, mae ymasiad yn cynhyrchu mwy o egni nag ymholltiad.</t>
-  </si>
-  <si>
     <t>adwaith_ymholltiad.png</t>
   </si>
   <si>
     <t>Cwblhewch yr hafaliad ar gyfer ymholltiad niwclear.</t>
   </si>
   <si>
-    <t>2 $\ce{^1_0n}$? &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt;  $\ce{^1_0n + ^1_0n}$</t>
-  </si>
-  <si>
     <t>adwaith_ymasiad.png</t>
   </si>
   <si>
@@ -609,6 +597,18 @@
   </si>
   <si>
     <t>$\ce{^2_1H +^3_1H -&gt; ^4_2He + ^1_0n}$</t>
+  </si>
+  <si>
+    <t>2 $\ce{^1_0n}$ &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt;  $\ce{^1_0n + ^1_0n}$</t>
+  </si>
+  <si>
+    <t>Angen tymheredd/egni  uchel iawn. &lt;br&gt; Angen gwasgedd uchel. &lt;br&gt; Angen i niwclysau gael digon o egni i fynd digon agos i'w gilydd a chyfuno.</t>
+  </si>
+  <si>
+    <t>Ymasiad ddim yn cynhyrchu gwastraff ymbelydrol gyda hanner oes hir.  &lt;br&gt;&lt;br&gt;Am bob cilogram, mae ymasiad yn cynhyrchu mwy o egni nag ymholltiad.</t>
+  </si>
+  <si>
+    <t>Mae gan y gwastraff ymbelydrol hanner oes hir iawn felly mae'n beryglus am amser hir iawn. &lt;br&gt; Mae'r gwastaff yn allyrru pelydriad (alffa/beta/gama) sy'n  ioneiddio'n gryf  neu gyda phŵer treiddio uchel.</t>
   </si>
 </sst>
 </file>
@@ -2045,13 +2045,13 @@
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>184</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2081,18 +2081,18 @@
         <v>174</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2100,25 +2100,25 @@
         <v>175</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C10" s="14"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5AE76CD-58DE-43F1-84E2-E8C0215092A9}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5695F384-082F-4621-AD6A-9C08C01399F3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="190">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -609,6 +609,12 @@
   </si>
   <si>
     <t>Mae gan y gwastraff ymbelydrol hanner oes hir iawn felly mae'n beryglus am amser hir iawn. &lt;br&gt; Mae'r gwastaff yn allyrru pelydriad (alffa/beta/gama) sy'n  ioneiddio'n gryf  neu gyda phŵer treiddio uchel.</t>
+  </si>
+  <si>
+    <t>Delwedd Cwestiwn</t>
+  </si>
+  <si>
+    <t>Delwedd Ateb</t>
   </si>
 </sst>
 </file>
@@ -976,7 +982,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>188</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1019,6 +1028,9 @@
         <v>11</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>105</v>
       </c>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5695F384-082F-4621-AD6A-9C08C01399F3}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666277CA-BA96-4801-8231-AFE519B465D6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="188">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -52,31 +52,15 @@
     <t>Delwedd</t>
   </si>
   <si>
-    <t>Beth yw uned pellter? 
-What is the unit for distance?</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
-    <t>Beth yw uned buanedd? 
-What is the unit for speed?</t>
-  </si>
-  <si>
     <t>m/s</t>
   </si>
   <si>
-    <t>Beth yw uned amser? 
-What is the unit for time?</t>
-  </si>
-  <si>
     <t>s</t>
   </si>
   <si>
-    <t>Beth yw uned cyflymiad? 
-What is the unit for acceleration?</t>
-  </si>
-  <si>
     <t>Disgrifiwch mudiant y bws yn rhan A</t>
   </si>
   <si>
@@ -116,15 +100,9 @@
     <t>Beth yw pellter brecio?</t>
   </si>
   <si>
-    <t>ê</t>
-  </si>
-  <si>
     <t>Y pellter mae'r cerbyd yn deithio cyn i'r gyrrwr bwyso'r brêc.</t>
   </si>
   <si>
-    <t>ô</t>
-  </si>
-  <si>
     <t>Y pellter mae'r cerbyd yn deithio ar ôl i'r gyrrwr bwyso'r brêc.</t>
   </si>
   <si>
@@ -615,6 +593,18 @@
   </si>
   <si>
     <t>Delwedd Ateb</t>
+  </si>
+  <si>
+    <t>Beth yw uned pellter?</t>
+  </si>
+  <si>
+    <t>Beth yw uned buanedd?</t>
+  </si>
+  <si>
+    <t>Beth yw uned amser?</t>
+  </si>
+  <si>
+    <t>Beth yw uned cyflymiad?</t>
   </si>
 </sst>
 </file>
@@ -982,175 +972,169 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>187</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1181,85 +1165,85 @@
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1289,65 +1273,65 @@
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1378,37 +1362,37 @@
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1448,138 +1432,138 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1612,43 +1596,43 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1728,142 +1712,142 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1913,43 +1897,43 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C6" s="14"/>
     </row>
@@ -2048,89 +2032,89 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C10" s="14"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666277CA-BA96-4801-8231-AFE519B465D6}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3CD258-42FC-42DB-B300-8C5334B3D27B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="187">
   <si>
     <t>Cwestiwn</t>
   </si>
   <si>
     <t>Ateb</t>
-  </si>
-  <si>
-    <t>Delwedd</t>
   </si>
   <si>
     <t>m</t>
@@ -972,169 +969,169 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1146,9 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="44.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1160,90 +1159,93 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
         <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
         <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
         <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1268,70 +1270,73 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
         <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1357,42 +1362,45 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="F2" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
         <v>110</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
         <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
         <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1412,14 +1420,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
     <col min="2" max="2" width="56.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,143 +1435,146 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1576,14 +1587,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
     <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1591,90 +1603,93 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="10"/>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
@@ -1692,14 +1707,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
     <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1707,147 +1723,150 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="14"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="14"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="B9" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="14"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="14"/>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>142</v>
-      </c>
       <c r="B13" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="10" t="s">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="B15" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="C15" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="B16" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1877,14 +1896,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
     <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1892,92 +1912,95 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B4" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="14"/>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
     </row>
@@ -2012,14 +2035,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.26953125" customWidth="1"/>
     <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2027,118 +2051,121 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B5" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="10" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="C9" s="14"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B10" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="14"/>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="C10" s="14"/>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
     </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
     </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3CD258-42FC-42DB-B300-8C5334B3D27B}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{830CB971-E616-4C67-B44C-D206D58988CC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -418,9 +418,6 @@
     <t>Pelydriad Cefndir Microdonnau Cosmig (CMBR) a Rhuddiad</t>
   </si>
   <si>
-    <t>Maen nhw i gyd yn dangos rhuddiad (llinellau wedi symud i ochr coch) oherwydd bod y galaethau yn symud i ffwrdd oddi wrthon ni. Mae'r Bydysawd wedi ehangu dros amser felly mae'n rhaid ei fod wedi dechrau o un pwynt (Y Glec Fawr).</t>
-  </si>
-  <si>
     <t>Beth yw'r pelydriad cefndir microdonnau cosmig (CMBR)?</t>
   </si>
   <si>
@@ -602,6 +599,9 @@
   </si>
   <si>
     <t>Beth yw uned cyflymiad?</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Maen nhw i gyd yn dangos rhuddiad (llinellau wedi symud i ochr coch) oherwydd bod y galaethau yn symud i ffwrdd oddi wrthon ni.&lt;/li&gt;&lt;li&gt;Mae'r Bydysawd wedi ehangu dros amser felly mae'n rhaid ei fod wedi dechrau o un pwynt (Y Glec Fawr).&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
@@ -969,15 +969,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
@@ -1159,10 +1159,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1260,6 +1260,8 @@
   <cols>
     <col min="1" max="1" width="53.81640625" customWidth="1"/>
     <col min="2" max="2" width="34.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1270,10 +1272,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1325,7 +1327,7 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>99</v>
@@ -1362,10 +1364,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1435,10 +1437,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1603,10 +1605,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1625,7 +1627,7 @@
         <v>122</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>119</v>
@@ -1641,13 +1643,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1723,10 +1725,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1755,39 +1757,39 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="14"/>
     </row>
@@ -1825,48 +1827,48 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="C14" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>134</v>
-      </c>
       <c r="C15" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1912,51 +1914,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>158</v>
       </c>
       <c r="C6" s="14"/>
     </row>
@@ -2051,97 +2053,97 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>164</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>176</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" s="14"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{830CB971-E616-4C67-B44C-D206D58988CC}"/>
+  <xr:revisionPtr revIDLastSave="359" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A84A01-FCCA-41E3-A71F-86E2D2FA06C0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -421,9 +421,6 @@
     <t>Beth yw'r pelydriad cefndir microdonnau cosmig (CMBR)?</t>
   </si>
   <si>
-    <t>Yn ystod y Glec Fawr cafodd pelydrau gama egni uchel a tonfedd fer eu rhyddhau. Wrth i'r Bydysawd ehangu mae tonfedd y pelydrau yma wedi ymestyn, erbyn heddiw mae eu tonfedd wedi ymestyn fel eu bod yn y rhan microdon o'r sbectrwm electromagnetig.</t>
-  </si>
-  <si>
     <t>CMBR.png</t>
   </si>
   <si>
@@ -601,14 +598,17 @@
     <t>Beth yw uned cyflymiad?</t>
   </si>
   <si>
-    <t>&lt;ul&gt;&lt;li&gt;Maen nhw i gyd yn dangos rhuddiad (llinellau wedi symud i ochr coch) oherwydd bod y galaethau yn symud i ffwrdd oddi wrthon ni.&lt;/li&gt;&lt;li&gt;Mae'r Bydysawd wedi ehangu dros amser felly mae'n rhaid ei fod wedi dechrau o un pwynt (Y Glec Fawr).&lt;/li&gt;&lt;/ul&gt;</t>
+    <t>&lt;ul&gt;&lt;li&gt;Maen nhw i gyd yn dangos rhuddiad (llinellau wedi symud i ochr coch) oherwydd bod y galaethau yn symud i ffwrdd oddi wrthon ni.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Mae'r Bydysawd wedi ehangu dros amser felly mae'n rhaid ei fod wedi dechrau o un pwynt (Y Glec Fawr).&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Yn ystod y Glec Fawr cafodd pelydrau gama egni uchel a tonfedd fer eu rhyddhau.&lt;/li&gt;&lt;br&gt;&lt;li&gt; Wrth i'r Bydysawd ehangu mae tonfedd y pelydrau yma wedi ymestyn.&lt;/li&gt;&lt;br&gt;&lt;li&gt; Erbyn heddiw mae eu tonfedd wedi ymestyn fel eu bod yn y rhan microdon o'r sbectrwm electromagnetig.&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -679,6 +679,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -713,7 +719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -736,6 +742,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,15 +976,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -985,7 +992,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -993,7 +1000,7 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -1001,7 +1008,7 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
@@ -1159,10 +1166,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1272,10 +1279,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1327,7 +1334,7 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>99</v>
@@ -1364,10 +1371,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
@@ -1437,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1605,10 +1612,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1627,7 +1634,7 @@
         <v>122</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>119</v>
@@ -1645,11 +1652,11 @@
       <c r="A5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1725,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1757,39 +1764,39 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" s="14"/>
     </row>
@@ -1827,48 +1834,48 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="C14" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="C15" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1914,51 +1921,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>157</v>
       </c>
       <c r="C6" s="14"/>
     </row>
@@ -2053,97 +2060,97 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>162</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>163</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="C5" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>175</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C10" s="14"/>
     </row>

--- a/CardiauFflachFfiseg.xlsx
+++ b/CardiauFflachFfiseg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="359" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A84A01-FCCA-41E3-A71F-86E2D2FA06C0}"/>
+  <xr:revisionPtr revIDLastSave="362" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760B6FBA-BB22-4488-9228-9A0BEC733C4C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1 Pellter, buanedd a chyflymi" sheetId="1" r:id="rId1"/>
@@ -490,12 +490,6 @@
     <t>Beth yw diffiniad hanner oes?</t>
   </si>
   <si>
-    <t>Os oes 800 o niwclysau ymbelydrol i gychwyn, sawl niwclysau ymbelydrol sydd yn weddill ar ôl 1 hanner oes?</t>
-  </si>
-  <si>
-    <t>Os oes 1400 o niwclysau ymbelydrol i gychwyn, sawl niwclysau ymbelydrol sydd yn weddill ar ôl 2 hanner oes?</t>
-  </si>
-  <si>
     <t>1400 $\Rightarrow$ 700 $\Rightarrow$ 350</t>
   </si>
   <si>
@@ -505,9 +499,6 @@
     <t>Beth fydd ffracsiwn y niwclysau ymbelydrol sy'n weddill  ar ôl 3 hanner oes?</t>
   </si>
   <si>
-    <t>1 $\Rightarrow \frac{1}{2}  \Rightarrow \frac{1}{4}$</t>
-  </si>
-  <si>
     <t>Mae gan isotop ymbelydrol hanner oes o 5 mlynedd. Beth yw'r canran sy'n weddill ar ôl 10 mlynedd?</t>
   </si>
   <si>
@@ -602,6 +593,15 @@
   </si>
   <si>
     <t>&lt;ul&gt;&lt;li&gt;Yn ystod y Glec Fawr cafodd pelydrau gama egni uchel a tonfedd fer eu rhyddhau.&lt;/li&gt;&lt;br&gt;&lt;li&gt; Wrth i'r Bydysawd ehangu mae tonfedd y pelydrau yma wedi ymestyn.&lt;/li&gt;&lt;br&gt;&lt;li&gt; Erbyn heddiw mae eu tonfedd wedi ymestyn fel eu bod yn y rhan microdon o'r sbectrwm electromagnetig.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>Os oes 800 o niwclysau ymbelydrol i gychwyn, sawl niwclews ymbelydrol sydd yn weddill ar ôl 1 hanner oes?</t>
+  </si>
+  <si>
+    <t>Os oes 1400 o niwclysau ymbelydrol i gychwyn, sawl niwclews ymbelydrol sydd yn weddill ar ôl 2 hanner oes?</t>
+  </si>
+  <si>
+    <t>1 $\Rightarrow \frac{1}{2}  \Rightarrow \frac{1}{4} \Rightarrow \frac{1}{8}$</t>
   </si>
 </sst>
 </file>
@@ -962,13 +962,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.26953125" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -976,45 +976,45 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>27</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>100</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>102</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>103</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>111</v>
       </c>
@@ -1150,15 +1150,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608DC02D-A3BC-4E94-A0C9-91816C3DAF43}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.453125" customWidth="1"/>
-    <col min="2" max="2" width="44.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="58.42578125" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1166,13 +1166,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>24</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>106</v>
       </c>
@@ -1263,15 +1263,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C49E91-841E-43E1-9E82-F658355D08D3}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" customWidth="1"/>
-    <col min="2" max="2" width="34.6328125" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C6" s="11"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1357,13 +1357,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808CBEAB-1A82-4D21-9D60-79ED5AE8D7ED}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" customWidth="1"/>
-    <col min="2" max="2" width="34.6328125" customWidth="1"/>
+    <col min="1" max="1" width="53.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1371,13 +1371,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>107</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>114</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="11"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C7" s="11"/>
     </row>
   </sheetData>
@@ -1430,13 +1430,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1444,13 +1444,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>70</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>97</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>75</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>81</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -1597,14 +1597,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="56.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1612,13 +1612,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>120</v>
       </c>
@@ -1629,18 +1629,18 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>123</v>
       </c>
@@ -1648,61 +1648,61 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="10"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
@@ -1717,14 +1717,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="56.54296875" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.5703125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,13 +1732,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>84</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>138</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>143</v>
       </c>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>144</v>
       </c>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C7" s="14"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>145</v>
       </c>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>88</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>90</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>92</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>95</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>139</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>129</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>131</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>133</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>135</v>
       </c>
@@ -1878,19 +1878,19 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
@@ -1906,14 +1906,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="56.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1921,115 +1921,115 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="10" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="14"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
@@ -2045,14 +2045,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="56.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2060,155 +2060,155 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C5" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B6" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C7" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="14"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="14"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>178</v>
-      </c>
       <c r="C10" s="14"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="10"/>
     </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="14"/>
     </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="14"/>
     </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
     </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
     </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
     </row>
